--- a/downloads/omnicraft_leather_cost_calculator.xlsx
+++ b/downloads/omnicraft_leather_cost_calculator.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор себестоимости" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Калькулятор себестоимости" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,10 +648,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -667,7 +667,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Честный расчёт расхода кожи, ловушки обрезков и стоимости нормы-часа</t>
+          <t>Честный расчёт расхода кожи, ловушки обрезков, комплектующих и стоимости нормы-часа</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>БЛОК 2: РАСХОД КОЖИ И ЛОВУШКА ОБРЕЗКОВ (КПИ)</t>
+          <t>БЛОК 2: РАСХОД КОЖИ И ЛОВУШКА ОБРЕЗКОВ</t>
         </is>
       </c>
     </row>
@@ -737,21 +737,21 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Коэффициент полезного раскроя (обычно 65%–80%)</t>
+          <t>Запас на потери в обрезках (% потерь при раскрое)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Фактический расход кожи с учётом раскроя (S факт.)</t>
+          <t>Фактический расход кожи с учётом обрезков (S факт.)</t>
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B10/B11</f>
+        <f>B10*(1+B11)</f>
         <v/>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>БЛОК 3: ФУРНИТУРА, ХИМИЯ И УПАКОВКА</t>
+          <t>БЛОК 3: ФУРНИТУРА</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Кнопки / хольнитены</t>
+          <t>Кнопки / кольца / хольнитены</t>
         </is>
       </c>
       <c r="B22" s="21" t="n">
@@ -881,14 +881,14 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>Нить плетеная вощеная (расход)</t>
+          <t>Карабины / рамки / полукольца (запасная строка)</t>
         </is>
       </c>
       <c r="B23" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D23" s="13">
         <f>B23*C23</f>
@@ -896,247 +896,334 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>ИТОГО ФУРНИТУРА (M фурн.)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="17">
+        <f>SUM(D20:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>БЛОК 4: НИТКИ И РАСХОДНИКИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Наименование расходника</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Цена за ед.</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Нить плетеная вощеная (расход на шов)</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" s="13">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Химия (клей, Tokonole, финиш, краска уреза)</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B29" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C29" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D24" s="13">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Брендовая упаковка (коробка, крафт, тишью)</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="D25" s="13">
-        <f>B25*C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>ИТОГО ФУРНИТУРА И ХИМИЯ (M компл.)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="17">
-        <f>SUM(D20:D25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>БЛОК 4: ВРЕМЯ МАСТЕРА И СТОИМОСТЬ ТРУДА (НОРМА-ЧАС)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Чистое время работы мастера над заказом (T)</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="n">
-        <v>6.5</v>
+      <c r="D29" s="13">
+        <f>B29*C29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Желаемая стоимость одного часа работы мастера (R)</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="n">
-        <v>500</v>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Армирующий материал / уплотнитель (запасная строка)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <f>B30*C30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>ИТОГО СЕБЕСТОИМОСТЬ РУЧНОГО ТРУДА (Cost труд)</t>
-        </is>
-      </c>
-      <c r="B31" s="17">
-        <f>B29*B30</f>
+          <t>ИТОГО НИТКИ И РАСХОДНИКИ (M расх.)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="17">
+        <f>SUM(D28:D30)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>БЛОК 5: АМОРТИЗАЦИЯ ИНСТРУМЕНТА И МЕЛКИЕ РАСХОДНИКИ</t>
+          <t>БЛОК 5: БРЕНДОВАЯ УПАКОВКА</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ставка износа инструмента и оборудования на 1 час</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="n">
-        <v>40</v>
+          <t>Брендовая упаковка (крафт-коробка, тишью, бирка, лента)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>ИТОГО УПАКОВКА (M упак.)</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>БЛОК 6: ВРЕМЯ МАСТЕРА И СТОИМОСТЬ ТРУДА (НОРМА-ЧАС)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Чистое время работы мастера над заказом (T)</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Ставка оплаты труда мастера за 1 час (R)</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>ИТОГО СЕБЕСТОИМОСТЬ РУЧНОГО ТРУДА (Cost труд)</t>
+        </is>
+      </c>
+      <c r="B40" s="17">
+        <f>B38*B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>БЛОК 7: АМОРТИЗАЦИЯ ИНСТРУМЕНТА И ОБОРУДОВАНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Ставка износа инструмента и оборудования на 1 час работы</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
           <t>ИТОГО ИЗНОС ИНСТРУМЕНТА НА ИЗДЕЛИЕ (Amort)</t>
         </is>
       </c>
-      <c r="B35" s="17">
-        <f>B29*B34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="B44" s="17">
+        <f>B38*B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>ИТОГОВЫЙ ДАШБОРД: ФИНАНСОВЫЙ ДИАГНОЗ ЗАКАЗА</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>1. Полная себестоимость изделия (Кожа + Фурнитура + Труд + Износ)</t>
-        </is>
-      </c>
-      <c r="B38" s="13">
-        <f>B16+D26+B31+B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>1. Полная себестоимость (Кожа + Фурнитура + Расходники + Упаковка + Труд + Износ)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B16+D24+D31+B35+B40+B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>2. Чистая прибыль мастерской сверх зарплаты (на развитие дела)</t>
         </is>
       </c>
-      <c r="B39" s="13">
-        <f>B6-B38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="B48" s="13">
+        <f>B6-B47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>3. Фактический заработок мастера на руки (Зарплата + Прибыль)</t>
         </is>
       </c>
-      <c r="B40" s="13">
-        <f>B31+B39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B49" s="13">
+        <f>B40+B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>4. Реальная ставка часа мастера по факту заказа (R факт.)</t>
         </is>
       </c>
-      <c r="B41" s="26">
-        <f>(B6-B16-D26-B35)/B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="B50" s="26">
+        <f>(B6-B16-D24-D31-B35-B44)/B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>5. Рентабельность изделия по чистой прибыли</t>
         </is>
       </c>
-      <c r="B42" s="27">
-        <f>B39/B6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="28">
-        <f>IF(B39&lt;0, "🔴 ИЛЛЮЗИЯ ПРИБЫЛИ: Заказ убыточен! Вы подарили заказчику свой труд и материалы.", IF(B41&lt;B30, "🟡 ВНИМАНИЕ: Прибыль есть, но реальный час (" &amp; ROUND(B41,0) &amp; " ₽/ч) ниже желаемого. Вы недооцениваете сложность.", "🟢 ОТЛИЧНЫЙ ЗАКАЗ: Изделие окупает материалы, ваш труд и приносит прибыль бизнесу."))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="B51" s="27">
+        <f>B48/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="28">
+        <f>IF(B48&lt;0, "🔴 ИЛЛЮЗИЯ ПРИБЫЛИ: Заказ убыточен! Вы подарили заказчику свой труд и материалы.", IF(B50&lt;B39, "🟡 ВНИМАНИЕ: Прибыль есть, но реальный час (" &amp; ROUND(B50,0) &amp; " ₽/ч) ниже базовой ставки. Вы недооцениваете сложность.", "🟢 ОТЛИЧНЫЙ ЗАКАЗ: Изделие окупает материалы, ваш труд и приносит прибыль бизнесу."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>💡 ПОЧЕМУ ТАБЛИЦА EXCEL — ЭТО ТОЛЬКО ПЕРВЫЙ ШАГ В МАСТЕРСКОЙ?</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="30" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>1. В Excel невозможно вести сквозной склад: остатки полукож и фурнитуры приходится пересчитывать вручную.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t>2. Таблицы путаются и ломаются, когда заказов становится больше 10 в месяц.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>3. В таблицах не видно резервов: взяли срочный заказ, а в субботу вечером закончился клей или не хватило бегунка.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="30" t="inlineStr"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="30" t="inlineStr"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>👉 OMNICRAFT ERP — Профессиональная локальная программа для кожевенников и мастеров:</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Сквозной учёт полукож по полезной площади с автоматическим списанием обрезков</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Верстак, статусы заказов, база постоянных клиентов и себестоимость в реальном времени</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Автономная работа на вашем ПК (Windows). Никаких облаков, подписок и утечек коммерческой тайны</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="31" t="inlineStr">
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>СКАЧАТЬ БЕСПЛАТНУЮ ВЕРСИЮ OMNICRAFT ERP НА ОФИЦИАЛЬНОМ САЙТЕ: https://omnicraft-erp.com</t>
         </is>
@@ -1144,31 +1231,34 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="21">
+  <mergeCells count="24">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/omnicraft_leather_cost_calculator.xlsx
+++ b/downloads/omnicraft_leather_cost_calculator.xlsx
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="28">
-        <f>IF(B48&lt;0, "🔴 ИЛЛЮЗИЯ ПРИБЫЛИ: Заказ убыточен! Вы подарили заказчику свой труд и материалы.", IF(B50&lt;B39, "🟡 ВНИМАНИЕ: Прибыль есть, но реальный час (" &amp; ROUND(B50,0) &amp; " ₽/ч) ниже базовой ставки. Вы недооцениваете сложность.", "🟢 ОТЛИЧНЫЙ ЗАКАЗ: Изделие окупает материалы, ваш труд и приносит прибыль бизнесу."))</f>
+        <f>IF(B48&lt;0, "🔴 ИЛЛЮЗИЯ ПРИБЫЛИ: Заказ убыточен! Вы подарили заказчику свой труд и материалы.", IF(B51&lt;0.15, "🟡 ВНИМАНИЕ: Прибыль есть, но чистая маржа (" &amp; ROUND(B51*100,1) &amp; "%) ниже 15%. Любой брак уведёт заказ в минус.", "🟢 ОТЛИЧНЫЙ ЗАКАЗ: Изделие окупает материалы, ваш труд и приносит прибыль бизнесу."))</f>
         <v/>
       </c>
     </row>
